--- a/ديمو/templates/04_المستخدمين.xlsx
+++ b/ديمو/templates/04_المستخدمين.xlsx
@@ -227,41 +227,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>المنظومة</author>
-  </authors>
-  <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>بيستخدم للدخول ولاستلام الإشعارات</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>admin, pmo, company, supervisor, exec_mgr, gm, tech_affairs, tech_office, planning, sector_head, presidency_head, committee, stores, finance</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>all = كل الجهات</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>كود الشركة/الرئاسة/القطاع/الإدارة/السنترال حسب نوع النطاق</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>اللي بيستلم بداله وقت الأجازات</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -705,7 +670,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -715,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -822,6 +786,51 @@
       <c r="A16" s="10" t="inlineStr">
         <is>
           <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>شرح الأعمدة</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>• [المستخدمين] الإيميل: بيستخدم للدخول ولاستلام الإشعارات</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>• [المستخدمين] الدور: admin, pmo, company, supervisor, exec_mgr, gm, tech_affairs, tech_office, planning, sector_head, presidency_head, committee, stores, finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>• [المستخدمين] نوع النطاق: all = كل الجهات</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>• [المستخدمين] كود النطاق: كود الشركة/الرئاسة/القطاع/الإدارة/السنترال حسب نوع النطاق</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>• [المستخدمين] إيميل البديل: اللي بيستلم بداله وقت الأجازات</t>
         </is>
       </c>
     </row>
@@ -836,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,6 +872,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>{"المستخدمين": [["م. محمد عليوة", "exec.arish@te.eg", "", "exec_mgr", "dept", "D-ARISH", ""], ["مسؤول مستخلصات بريدج", "invoices@bridge.com", "", "company", "company", "CO-BRIDGE", ""]]}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ديمو/templates/04_المستخدمين.xlsx
+++ b/ديمو/templates/04_المستخدمين.xlsx
@@ -536,22 +536,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>الإيميل *</t>
+          <t>البريد الإلكتروني *</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>الموبايل</t>
+          <t>رقم الهاتف المحمول</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>الدور *</t>
+          <t>الدور الوظيفي *</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>نوع النطاق *</t>
+          <t>نوع نطاق الصلاحية *</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>إيميل البديل</t>
+          <t>البريد الإلكتروني للبديل</t>
         </is>
       </c>
     </row>
@@ -662,10 +662,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="D3:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="قيمة غير مسموحة" error="اختار من القائمة" type="list">
+    <dataValidation sqref="D3:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="قيمة غير مسموحة" error="يرجى الاختيار من القائمة" type="list">
       <formula1>"admin,pmo,company,supervisor,exec_mgr,gm,tech_affairs,tech_office,planning,sector_head,presidency_head,committee,stores,finance"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="قيمة غير مسموحة" error="اختار من القائمة" type="list">
+    <dataValidation sqref="E3:E5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="قيمة غير مسموحة" error="يرجى الاختيار من القائمة" type="list">
       <formula1>"all,company,presidency,sector,gdept,dept,central"</formula1>
     </dataValidation>
   </dataValidations>
@@ -688,21 +688,21 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>قالب المستخدمين والصلاحيات</t>
+          <t>نموذج المستخدمين والصلاحيات</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>الغرض: إنشاء حسابات المستخدمين مع الدور والنطاق.</t>
+          <t>الغرض: إنشاء حسابات المستخدمين مع الدور الوظيفي ونطاق الصلاحية.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>مين بيرفعه: مدير النظام.</t>
+          <t>الجهة المسؤولة عن الرفع: مدير النظام.</t>
         </is>
       </c>
     </row>
@@ -712,28 +712,28 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>قواعد الملء</t>
+          <t>قواعد تعبئة البيانات</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>• كل مستخدم بيوصله إيميل دعوة يحدد منه كلمة السر.</t>
+          <t>• تُرسل إلى كل مستخدم دعوة بالبريد الإلكتروني لتعيين كلمة المرور.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>• النطاق بيحدد هو يشوف إيه: مدير التنفيذ = إدارته المختصة، المدير العام = إدارته العامة، وهكذا.</t>
+          <t>• يحدد نطاق الصلاحية البيانات التي يطّلع عليها المستخدم: مدير التنفيذ = إدارته المختصة، والمدير العام = إدارته العامة، وهكذا.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>• ممكن تكرر نفس الإيميل في أكتر من صف لو الشخص ليه أكتر من نطاق.</t>
+          <t>• يمكن تكرار البريد الإلكتروني نفسه في أكثر من صف إذا كان للمستخدم أكثر من نطاق صلاحية.</t>
         </is>
       </c>
     </row>
@@ -743,49 +743,49 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>قواعد عامة لكل القوالب</t>
+          <t>قواعد عامة لجميع النماذج</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>• ما تغيّرش أسماء الشيتات ولا ترتيب الأعمدة ولا الصف التاني (اسم العمود التقني).</t>
+          <t>• لا يجوز تغيير أسماء أوراق العمل أو ترتيب الأعمدة أو الصف الثاني (الاسم التقني للعمود).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>• العمود اللي عليه * إلزامي. الأعمدة اللي فيها قائمة لازم تختار منها.</t>
+          <t>• العمود المميز بعلامة * إلزامي، ويجب الاختيار من القائمة في الأعمدة التي تتضمن قائمة اختيار.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>• الصفوف الرمادي أمثلة — امسحها قبل الرفع.</t>
+          <t>• الصفوف الرمادية أمثلة توضيحية — يرجى حذفها قبل الرفع.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>• الأرقام من غير فواصل أو عملة. التواريخ يوم/شهر/سنة.</t>
+          <t>• تُدخل الأرقام دون فواصل أو رمز عملة، والتواريخ بصيغة يوم/شهر/سنة.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>• عند الرفع السيستم بيعرض معاينة بكل صف وأخطاؤه قبل الحفظ — مفيش حاجة بتتحفظ قبل ما توافق.</t>
+          <t>• عند الرفع تعرض المنظومة نتيجة المراجعة لكل صف وأخطاءه قبل الحفظ — ولا يُحفظ أي سجل قبل «اعتماد الاستيراد».</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
+          <t>• إصدار النموذج: 1.0 — إذا كان النموذج قديماً ستطلب المنظومة تحميل الإصدار الأحدث.</t>
         </is>
       </c>
     </row>
@@ -795,42 +795,42 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>شرح الأعمدة</t>
+          <t>إيضاح الأعمدة</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>• [المستخدمين] الإيميل: بيستخدم للدخول ولاستلام الإشعارات</t>
+          <t>• [المستخدمين] البريد الإلكتروني: يُستخدم لتسجيل الدخول واستلام التنبيهات</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>• [المستخدمين] الدور: admin, pmo, company, supervisor, exec_mgr, gm, tech_affairs, tech_office, planning, sector_head, presidency_head, committee, stores, finance</t>
+          <t>• [المستخدمين] الدور الوظيفي: admin, pmo, company, supervisor, exec_mgr, gm, tech_affairs, tech_office, planning, sector_head, presidency_head, committee, stores, finance</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>• [المستخدمين] نوع النطاق: all = كل الجهات</t>
+          <t>• [المستخدمين] نوع نطاق الصلاحية: all = جميع الجهات</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>• [المستخدمين] كود النطاق: كود الشركة/الرئاسة/القطاع/الإدارة/السنترال حسب نوع النطاق</t>
+          <t>• [المستخدمين] كود النطاق: كود الشركة المنفذة/رئاسة القطاعات/القطاع/الإدارة/السنترال حسب نوع نطاق الصلاحية</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>• [المستخدمين] إيميل البديل: اللي بيستلم بداله وقت الأجازات</t>
+          <t>• [المستخدمين] البريد الإلكتروني للبديل: المستخدم البديل خلال فترات الإجازة</t>
         </is>
       </c>
     </row>

--- a/ديمو/templates/04_المستخدمين.xlsx
+++ b/ديمو/templates/04_المستخدمين.xlsx
@@ -605,7 +605,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>م. محمد عليوة</t>
+          <t>مثال — م. محمد عليوة</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -634,7 +634,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>مسؤول مستخلصات بريدج</t>
+          <t>مثال — مسؤول مستخلصات بريدج</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"المستخدمين": [["م. محمد عليوة", "exec.arish@te.eg", "", "exec_mgr", "dept", "D-ARISH", ""], ["مسؤول مستخلصات بريدج", "invoices@bridge.com", "", "company", "company", "CO-BRIDGE", ""]]}</t>
+          <t>{"المستخدمين": [["مثال — م. محمد عليوة", "exec.arish@te.eg", "", "exec_mgr", "dept", "D-ARISH", ""], ["مثال — مسؤول مستخلصات بريدج", "invoices@bridge.com", "", "company", "company", "CO-BRIDGE", ""]]}</t>
         </is>
       </c>
     </row>
